--- a/B-6/Assets/Resources/Json/skill/SkillDamage/skill_damage_data.xlsx
+++ b/B-6/Assets/Resources/Json/skill/SkillDamage/skill_damage_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\b3\B-6\Assets\Resources\Json\skill\SkillCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\削除\B-6\Assets\Resources\Json\skill\SkillDamage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1961BFB3-370A-4160-9818-8479FA3EB77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6707C9-462F-4EC7-9183-793EA938B397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -135,9 +133,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,9 +173,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -210,9 +208,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -245,9 +260,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,9 +454,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,37 +464,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -657,27 +710,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -694,23 +746,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
-    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>